--- a/docs/downloads/经营分_山西省区__山西南片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_山西省区__山西南片区_2026-10-18.xlsx
@@ -862,22 +862,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>6601141576905279495</t>
+          <t>7205785499250739240</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7天优品（临汾生龙国际鼓楼东大街店）</t>
+          <t>非繁城品酒店(运城南风广场地矿店)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7天优品酒店(临汾鼓楼东大街店)</t>
+          <t>非繁城品(运城南风广场地矿店)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
         <v>30</v>
@@ -915,7 +915,7 @@
         <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R4" t="n">
         <v>30</v>
@@ -950,22 +950,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>7412164612600924196</t>
+          <t>7503744484267313152</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>丽怡酒店（运城星河广场店）</t>
+          <t>麗枫酒店（临汾洪洞大槐树店）</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>丽怡酒店(运城星河广场店)</t>
+          <t>麗枫酒店(临汾洪洞大槐树景区店)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -977,7 +977,7 @@
         <v>87</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -997,13 +997,13 @@
         <v>30</v>
       </c>
       <c r="O5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P5" t="n">
         <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R5" t="n">
         <v>30</v>
@@ -1038,22 +1038,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>7205785499250739240</t>
+          <t>6601141576905279495</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>非繁城品酒店(运城南风广场地矿店)</t>
+          <t>7天优品（临汾生龙国际鼓楼东大街店）</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>非繁城品(运城南风广场地矿店)</t>
+          <t>7天优品酒店(临汾鼓楼东大街店)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>10</v>
       </c>
       <c r="M6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N6" t="n">
         <v>30</v>
@@ -1091,7 +1091,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R6" t="n">
         <v>30</v>
@@ -1126,34 +1126,34 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>7503744484267313152</t>
+          <t>7581298849579436066</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>麗枫酒店（临汾洪洞大槐树店）</t>
+          <t>7天智选酒店（运城七彩盐湖盬街店）</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>麗枫酒店(临汾洪洞大槐树景区店)</t>
+          <t>7天智选酒店(运城七彩盐湖盬街店)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
       <c r="M7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N7" t="n">
         <v>30</v>
@@ -1179,7 +1179,7 @@
         <v>30</v>
       </c>
       <c r="Q7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R7" t="n">
         <v>30</v>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>7581298849579436066</t>
+          <t>7233737738418145340</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7天智选酒店（运城七彩盐湖盬街店）</t>
+          <t>IU酒店(运城永济迎宾路福茂骨科医院店)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7天智选酒店(运城七彩盐湖盬街店)</t>
+          <t>IU酒店(运城永济迎宾路福茂骨科医院店)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1241,7 +1241,7 @@
         <v>90</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1307,29 +1307,29 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>7233737738418145340</t>
+          <t>7411758004451674152</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>IU酒店(运城永济迎宾路福茂骨科医院店)</t>
+          <t>维也纳国际酒店（5.0河津龙门大道店）</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>IU酒店(运城永济迎宾路福茂骨科医院店)</t>
+          <t>维也纳国际酒店(河津龙门大道店)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>90</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1343,13 +1343,13 @@
         <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N9" t="n">
         <v>30</v>
       </c>
       <c r="O9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P9" t="n">
         <v>30</v>
@@ -1395,17 +1395,17 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>7411758004451674152</t>
+          <t>7412164612600924196</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（5.0河津龙门大道店）</t>
+          <t>丽怡酒店（运城星河广场店）</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(河津龙门大道店)</t>
+          <t>丽怡酒店(运城星河广场店)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="I10" t="n">
-        <v>-5</v>
+        <v>5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="N10" t="n">
         <v>30</v>
@@ -1443,7 +1443,7 @@
         <v>30</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R10" t="n">
         <v>30</v>
@@ -2473,7 +2473,7 @@
         <v>95</v>
       </c>
       <c r="I22" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -2891,17 +2891,17 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7325070761364817961</t>
+          <t>7247831339464919078</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IU酒店（临汾铝锅巷迎春南街店）</t>
+          <t>维也纳酒店（5.0霍州署香江城购物广场店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>IU酒店(临汾迎春南街店)</t>
+          <t>维也纳酒店(霍州香江城店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2910,7 +2910,7 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2927,7 +2927,7 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
@@ -2979,33 +2979,33 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7039541568272861198</t>
+          <t>7325070761364817961</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>喆啡酒店（临汾生龙国际平阳广场店）</t>
+          <t>IU酒店（临汾铝锅巷迎春南街店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>喆啡酒店(临汾生龙国际平阳广场店)</t>
+          <t>IU酒店(临汾迎春南街店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>105</v>
       </c>
       <c r="I28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -3021,13 +3021,13 @@
         <v>30</v>
       </c>
       <c r="O28" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P28" t="n">
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3062,22 +3062,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>晋城市</t>
+          <t>临汾市</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7498181324855838755</t>
+          <t>7039541568272861198</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0晋城经济开发区兰花路店）</t>
+          <t>喆啡酒店（临汾生龙国际平阳广场店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>维也纳酒店(晋城经济开发区兰花路店)</t>
+          <t>喆啡酒店(临汾生龙国际平阳广场店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3089,7 +3089,7 @@
         <v>105</v>
       </c>
       <c r="I29" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3150,22 +3150,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>运城市</t>
+          <t>晋城市</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7493356975233861671</t>
+          <t>7498181324855838755</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0深化版运城北站吾悦广场店）</t>
+          <t>维也纳酒店（5.0晋城经济开发区兰花路店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>维也纳酒店(运城北站店)</t>
+          <t>维也纳酒店(晋城经济开发区兰花路店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3177,11 +3177,11 @@
         <v>105</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3197,13 +3197,13 @@
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3243,17 +3243,17 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7234789456606136353</t>
+          <t>7493356975233861671</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>麗枫酒店(运城永乐街高铁站店)</t>
+          <t>维也纳酒店（5.0深化版运城北站吾悦广场店）</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>麗枫酒店(运城永乐街店)</t>
+          <t>维也纳酒店(运城北站店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3285,13 +3285,13 @@
         <v>30</v>
       </c>
       <c r="O31" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P31" t="n">
         <v>30</v>
       </c>
       <c r="Q31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R31" t="n">
         <v>30</v>
@@ -3326,22 +3326,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>临汾市</t>
+          <t>运城市</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>7247831339464919078</t>
+          <t>7234789456606136353</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0霍州署香江城购物广场店）</t>
+          <t>麗枫酒店(运城永乐街高铁站店)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>维也纳酒店(霍州香江城店)</t>
+          <t>麗枫酒店(运城永乐街店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3350,14 +3350,14 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>稳房源,提质量</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -3367,19 +3367,19 @@
         <v>10</v>
       </c>
       <c r="M32" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N32" t="n">
         <v>30</v>
       </c>
       <c r="O32" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P32" t="n">
         <v>30</v>
       </c>
       <c r="Q32" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R32" t="n">
         <v>30</v>
@@ -3705,7 +3705,7 @@
         <v>120</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
